--- a/outputs/evaluation/requirement/design/v2/gemini-3-1-flash-lite/CF_M01/first/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-1-flash-lite/CF_M01/first/CF_M01_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.7</v>
       </c>
       <c r="D13" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9323</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow authorized users to list actions performed on platform entities.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -773,10 +777,6 @@
 platform entities</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -807,10 +807,6 @@
           <t>The system shall allow authorized users to list system playlogs.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -824,10 +820,6 @@
           <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -858,10 +850,6 @@
           <t>The system shall allow authorized users to list player connections.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -875,10 +863,6 @@
           <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,10 +893,6 @@
           <t>The system shall store player connections.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -926,10 +906,6 @@
           <t>System saves player connections</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -965,9 +941,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>QR</t>
@@ -991,8 +964,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1028,9 +999,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1054,8 +1022,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1091,9 +1057,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1107,14 +1070,11 @@
           <t>The system scales automatically as they go increasing the data.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M01_R24</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1145,14 +1105,11 @@
           <t>Each action must contain a date, client, user, and assigned player.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1166,14 +1123,11 @@
           <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1204,10 +1158,6 @@
           <t>The system shall store playlogs from the players.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1221,10 +1171,6 @@
           <t>System saves the players' playlogs</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1255,14 +1201,11 @@
           <t>Actions visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_14</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1276,14 +1219,11 @@
           <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1314,14 +1254,11 @@
           <t>Connections visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1335,14 +1272,11 @@
           <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1373,14 +1307,11 @@
           <t>The system must allow viewing all details of the playlog.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1394,14 +1325,11 @@
           <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1432,14 +1360,11 @@
           <t>Playlogs visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1453,14 +1378,11 @@
           <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1491,14 +1413,11 @@
           <t>Each playlog must contain a date, client, and assigned player.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1512,14 +1431,11 @@
           <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M01_R01</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1555,9 +1471,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1582,8 +1495,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1614,10 +1525,6 @@
           <t>The system shall store actions performed on the platform.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1631,10 +1538,6 @@
           <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1665,14 +1568,11 @@
           <t>All actions must be performed on a platform entity.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1686,14 +1586,11 @@
           <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1724,14 +1621,11 @@
           <t>Each connection must contain a date, client, and assigned player.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1745,14 +1639,11 @@
           <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1788,9 +1679,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1804,14 +1692,11 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M01_R018</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1847,9 +1732,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1874,8 +1756,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1906,14 +1786,11 @@
           <t>The connection status can only be 'connected' or 'not connected'.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1927,14 +1804,11 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
